--- a/SPEC MyBook PRO M5.xlsx
+++ b/SPEC MyBook PRO M5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Downloads\Spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Desktop\axioo_b2g\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBA5426-32E0-45B7-A42E-09C8A9669D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775D55D7-4D6B-4C8C-A778-88E2C81B2BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EC415980-61FC-4EAB-8AD9-40FD9C97A95F}"/>
   </bookViews>
@@ -167,13 +167,90 @@
     <t>1x MicroSD Card</t>
   </si>
   <si>
+    <t>1.43Kg</t>
+  </si>
+  <si>
+    <t>321 (W) x 22 (D) x 206 (H) mm</t>
+  </si>
+  <si>
+    <t>1x M.2 2280 PCIe NVMe up to Gen4x4</t>
+  </si>
+  <si>
+    <t>WiFi 6 AX101 a/b/g/n/ac/ax</t>
+  </si>
+  <si>
+    <t>MyBook PRO M5</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i5-1334U(10 Cores, 12 Threads, TDP : 15W)</t>
+  </si>
+  <si>
+    <t>Intel® Iris® Xe Graphics eligible</t>
+  </si>
+  <si>
+    <t>2x SODIMM DDR4  up to Dual Channel 64 GB 3200 MT/s</t>
+  </si>
+  <si>
+    <t>2Mp 1080p 30fps with Privacy Shutter</t>
+  </si>
+  <si>
+    <t>Embedded 3 cells Lithium-ion polymer battery pack, 11.5V, 51.98Wh, 4500mAh</t>
+  </si>
+  <si>
+    <t>FHD 1920x1080 16:9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Performance-Core</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 2 Cores, 4 Threads, 1.3GHz Base, 4.6GHz Turbo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Efficient-Core</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 8 Cores, 8 Threads, 0.9GHz Base, 3.4GHz Turbo</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t>180</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -183,7 +260,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -192,87 +269,12 @@
       <t xml:space="preserve"> Hinge Rotate</t>
     </r>
   </si>
-  <si>
-    <t>1.43Kg</t>
-  </si>
-  <si>
-    <t>321 (W) x 22 (D) x 206 (H) mm</t>
-  </si>
-  <si>
-    <t>1x M.2 2280 PCIe NVMe up to Gen4x4</t>
-  </si>
-  <si>
-    <t>WiFi 6 AX101 a/b/g/n/ac/ax</t>
-  </si>
-  <si>
-    <t>MyBook PRO M5</t>
-  </si>
-  <si>
-    <t>Intel® Core™ i5-1334U(10 Cores, 12 Threads, TDP : 15W)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Efficient-Core</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 8 Cores, 8 Threads, 0.9GHz Base, 3.4GHz Turbo</t>
-    </r>
-  </si>
-  <si>
-    <t>Intel® Iris® Xe Graphics eligible</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Performance-Core</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 2 Cores, 4 Threads, 1.3GHz Base, 4.6GHz Turbo</t>
-    </r>
-  </si>
-  <si>
-    <t>2x SODIMM DDR4  up to Dual Channel 64 GB 3200 MT/s</t>
-  </si>
-  <si>
-    <t>2Mp 1080p 30fps with Privacy Shutter</t>
-  </si>
-  <si>
-    <t>Embedded 3 cells Lithium-ion polymer battery pack, 11.5V, 51.98Wh, 4500mAh</t>
-  </si>
-  <si>
-    <t>FHD 1920x1080 16:9</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +291,25 @@
     </font>
     <font>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -296,52 +317,54 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="9"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -349,23 +372,11 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -457,98 +468,99 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -868,14 +880,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F7ED28-56AA-4B0E-8F1C-66DBC3E2187D}">
   <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -883,298 +896,298 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="8"/>
+      <c r="B5" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13.2">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="24"/>
-      <c r="B5" s="5" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="18"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="19"/>
+      <c r="B18" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="19"/>
+      <c r="B19" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="19"/>
+      <c r="B20" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="19"/>
+      <c r="B21" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="19"/>
+      <c r="B22" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="19"/>
+      <c r="B23" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="9"/>
+      <c r="B25" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="25"/>
-      <c r="B6" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="8" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="19"/>
+      <c r="B27" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="19"/>
+      <c r="B29" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="19"/>
+      <c r="B31" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="13.2">
+      <c r="A34" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="9"/>
+      <c r="B37" s="26" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="27"/>
-      <c r="B22" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="25"/>
-      <c r="B25" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="27"/>
-      <c r="B29" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="27"/>
-      <c r="B31" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15">
-      <c r="A34" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="25"/>
-      <c r="B37" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="29"/>
-      <c r="B38" s="11"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="18"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="29"/>
-      <c r="B39" s="11"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="18"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="29"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="18"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="30"/>
-      <c r="B41" s="16"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="29"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="30"/>
-      <c r="B43" s="1"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="30"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="30"/>
-      <c r="B44" s="1"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="30"/>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="31"/>
-      <c r="B45" s="17"/>
+      <c r="B45" s="32"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="32"/>
+      <c r="A46" s="33"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="B47" s="16"/>
+      <c r="B47" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1193,6 +1206,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F1C94A586F6A64AA956C7CA2AB05C9B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f4315622f99eaf65af18b57ec807dec5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f82bd302-08e5-41cf-ac7e-929bc680f927" xmlns:ns3="189b1353-a086-487c-981c-f6344e352306" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce1289053e2708c538c907a002d6effc" ns2:_="" ns3:_="">
     <xsd:import namespace="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
@@ -1427,27 +1460,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A6F78-C6A5-4814-9F77-49EBAB421611}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
+    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ADF5931-48CC-464D-A637-909FE02062BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B299FD4-F79A-4D6D-9ABF-B836F94396AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1464,23 +1496,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ADF5931-48CC-464D-A637-909FE02062BC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A6F78-C6A5-4814-9F77-49EBAB421611}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
-    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>